--- a/Sample_run/1/student/Control/TC6/GradeDetail.xlsx
+++ b/Sample_run/1/student/Control/TC6/GradeDetail.xlsx
@@ -164,7 +164,10 @@
     <x:t>Server</x:t>
   </x:si>
   <x:si>
-    <x:t>PASS</x:t>
+    <x:t>(MISSING - not captured)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FAIL</x:t>
   </x:si>
   <x:si>
     <x:t>SYN, ACK</x:t>
@@ -191,34 +194,16 @@
     <x:t>{"StudentId":"Sabc","Name":null,"Major":null,"Year":null,"GPA":null,"Status":"error","Message":"Invalid student ID format. Expected: S followed by 3 digits"}</x:t>
   </x:si>
   <x:si>
-    <x:t>{"StudentId":"Sabc","Name":null,"Major":null,"Year":null,"GPA":null,"Status":"error","Message":"Student not found"}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PARTIAL</x:t>
-  </x:si>
-  <x:si>
     <x:t>FIN, ACK</x:t>
   </x:si>
   <x:si>
     <x:t>Closing connection (FIN-ACK)</x:t>
   </x:si>
   <x:si>
-    <x:t>Server closing connection</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Client closing connection</x:t>
-  </x:si>
-  <x:si>
     <x:t>S111</x:t>
   </x:si>
   <x:si>
     <x:t>{"StudentId":"S111","Name":null,"Major":null,"Year":null,"GPA":null,"Status":"error","Message":"Student not found"}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(MISSING - not captured)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FAIL</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -245,22 +230,12 @@
       <x:family val="2"/>
     </x:font>
   </x:fonts>
-  <x:fills count="5">
+  <x:fills count="3">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FF90EE90"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFFF00"/>
-      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -287,7 +262,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="5">
+  <x:cellStyleXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -297,14 +272,8 @@
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="5">
+  <x:cellXfs count="3">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -314,14 +283,6 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -995,10 +956,10 @@
     <x:col min="9" max="9" width="10.853482" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="15.139196" style="0" customWidth="1"/>
     <x:col min="11" max="11" width="23.424911" style="0" customWidth="1"/>
-    <x:col min="12" max="12" width="29.996339" style="0" customWidth="1"/>
+    <x:col min="12" max="12" width="10.996339" style="0" customWidth="1"/>
     <x:col min="13" max="13" width="16.424911" style="0" customWidth="1"/>
     <x:col min="14" max="14" width="14.424911" style="0" customWidth="1"/>
-    <x:col min="15" max="15" width="108.853482" style="0" customWidth="1"/>
+    <x:col min="15" max="15" width="10.567768" style="0" customWidth="1"/>
     <x:col min="16" max="16" width="16.424911" style="0" customWidth="1"/>
     <x:col min="17" max="17" width="14.424911" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="14.139196" style="0" customWidth="1"/>
@@ -1092,28 +1053,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K2" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N2" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O2" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P2" s="0">
-        <x:v>35918</x:v>
-      </x:c>
-      <x:c r="Q2" s="0">
-        <x:v>4000</x:v>
+      <x:c r="P2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q2" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R2" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:18">
@@ -1133,10 +1094,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
         <x:v>17</x:v>
@@ -1148,28 +1109,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="L3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q3" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R3" s="2" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="L3" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="M3" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="N3" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="O3" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P3" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q3" s="0">
-        <x:v>35918</x:v>
-      </x:c>
-      <x:c r="R3" s="2" t="s">
-        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:18">
@@ -1189,10 +1150,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H4" s="0" t="s">
         <x:v>17</x:v>
@@ -1204,28 +1165,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K4" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O4" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P4" s="0">
-        <x:v>35918</x:v>
-      </x:c>
-      <x:c r="Q4" s="0">
-        <x:v>4000</x:v>
+      <x:c r="P4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q4" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R4" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:18">
@@ -1245,13 +1206,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
         <x:v>46</x:v>
@@ -1260,28 +1221,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="P5" s="0">
-        <x:v>35918</x:v>
-      </x:c>
-      <x:c r="Q5" s="0">
-        <x:v>4000</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q5" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R5" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:18">
@@ -1301,10 +1262,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H6" s="0" t="s">
         <x:v>17</x:v>
@@ -1316,28 +1277,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K6" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N6" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P6" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q6" s="0">
-        <x:v>35918</x:v>
+      <x:c r="P6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q6" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R6" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:18">
@@ -1357,13 +1318,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H7" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="I7" s="0" t="s">
         <x:v>47</x:v>
@@ -1372,28 +1333,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K7" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M7" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N7" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O7" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="P7" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q7" s="0">
-        <x:v>35918</x:v>
-      </x:c>
-      <x:c r="R7" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q7" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R7" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:18">
@@ -1413,10 +1374,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H8" s="0" t="s">
         <x:v>17</x:v>
@@ -1428,28 +1389,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N8" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O8" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P8" s="0">
-        <x:v>35918</x:v>
-      </x:c>
-      <x:c r="Q8" s="0">
-        <x:v>4000</x:v>
+      <x:c r="P8" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q8" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R8" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:18">
@@ -1469,10 +1430,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
         <x:v>17</x:v>
@@ -1484,28 +1445,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K9" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N9" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O9" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P9" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q9" s="0">
-        <x:v>35918</x:v>
-      </x:c>
-      <x:c r="R9" s="3" t="s">
-        <x:v>58</x:v>
+      <x:c r="P9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q9" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R9" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:18">
@@ -1525,10 +1486,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H10" s="0" t="s">
         <x:v>17</x:v>
@@ -1540,28 +1501,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O10" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P10" s="0">
-        <x:v>35918</x:v>
-      </x:c>
-      <x:c r="Q10" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R10" s="3" t="s">
-        <x:v>58</x:v>
+      <x:c r="P10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q10" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R10" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:18">
@@ -1581,10 +1542,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
         <x:v>17</x:v>
@@ -1596,28 +1557,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K11" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M11" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N11" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O11" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P11" s="0">
-        <x:v>35918</x:v>
-      </x:c>
-      <x:c r="Q11" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R11" s="3" t="s">
-        <x:v>58</x:v>
+      <x:c r="P11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q11" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R11" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:18">
@@ -1637,10 +1598,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H12" s="0" t="s">
         <x:v>17</x:v>
@@ -1652,28 +1613,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K12" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N12" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O12" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P12" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q12" s="0">
-        <x:v>35918</x:v>
-      </x:c>
-      <x:c r="R12" s="3" t="s">
-        <x:v>58</x:v>
+      <x:c r="P12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q12" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R12" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:18">
@@ -1708,28 +1669,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L13" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M13" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N13" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O13" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P13" s="0">
-        <x:v>54214</x:v>
-      </x:c>
-      <x:c r="Q13" s="0">
-        <x:v>4000</x:v>
+      <x:c r="P13" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q13" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R13" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:18">
@@ -1749,10 +1710,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
         <x:v>17</x:v>
@@ -1764,28 +1725,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="L14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="M14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="N14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="O14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q14" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R14" s="2" t="s">
         <x:v>49</x:v>
-      </x:c>
-      <x:c r="L14" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="M14" s="0" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="N14" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="O14" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="P14" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q14" s="0">
-        <x:v>54214</x:v>
-      </x:c>
-      <x:c r="R14" s="2" t="s">
-        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:18">
@@ -1805,10 +1766,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
         <x:v>17</x:v>
@@ -1820,28 +1781,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L15" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M15" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N15" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O15" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P15" s="0">
-        <x:v>54214</x:v>
-      </x:c>
-      <x:c r="Q15" s="0">
-        <x:v>4000</x:v>
+      <x:c r="P15" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q15" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R15" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:18">
@@ -1861,13 +1822,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G16" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I16" s="0" t="s">
         <x:v>46</x:v>
@@ -1876,28 +1837,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K16" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L16" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M16" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N16" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O16" s="0" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="P16" s="0">
-        <x:v>54214</x:v>
-      </x:c>
-      <x:c r="Q16" s="0">
-        <x:v>4000</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P16" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q16" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R16" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:18">
@@ -1917,10 +1878,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
         <x:v>17</x:v>
@@ -1932,28 +1893,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L17" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M17" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N17" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O17" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P17" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q17" s="0">
-        <x:v>54214</x:v>
+      <x:c r="P17" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q17" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R17" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:18">
@@ -1973,13 +1934,13 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H18" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="I18" s="0" t="s">
         <x:v>47</x:v>
@@ -1988,28 +1949,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K18" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L18" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M18" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N18" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O18" s="0" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="P18" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q18" s="0">
-        <x:v>54214</x:v>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="P18" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q18" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R18" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:18">
@@ -2029,10 +1990,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G19" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H19" s="0" t="s">
         <x:v>17</x:v>
@@ -2044,28 +2005,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K19" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L19" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M19" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N19" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O19" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P19" s="0">
-        <x:v>54214</x:v>
-      </x:c>
-      <x:c r="Q19" s="0">
-        <x:v>4000</x:v>
+      <x:c r="P19" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q19" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R19" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:18">
@@ -2085,10 +2046,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G20" s="0" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="G20" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
       <x:c r="H20" s="0" t="s">
         <x:v>17</x:v>
@@ -2100,28 +2061,28 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K20" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L20" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M20" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N20" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O20" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P20" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q20" s="0">
-        <x:v>54214</x:v>
-      </x:c>
-      <x:c r="R20" s="3" t="s">
-        <x:v>58</x:v>
+      <x:c r="P20" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q20" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R20" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:18">
@@ -2141,10 +2102,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
         <x:v>17</x:v>
@@ -2156,28 +2117,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L21" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M21" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N21" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O21" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P21" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="Q21" s="0">
-        <x:v>54214</x:v>
+      <x:c r="P21" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q21" s="0" t="s">
+        <x:v>17</x:v>
       </x:c>
       <x:c r="R21" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:18">
@@ -2197,10 +2158,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G22" s="0" t="s">
         <x:v>59</x:v>
-      </x:c>
-      <x:c r="G22" s="0" t="s">
-        <x:v>60</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
         <x:v>17</x:v>
@@ -2212,28 +2173,28 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L22" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="M22" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="N22" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="O22" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="P22" s="0">
-        <x:v>54214</x:v>
-      </x:c>
-      <x:c r="Q22" s="0">
-        <x:v>4000</x:v>
-      </x:c>
-      <x:c r="R22" s="3" t="s">
-        <x:v>58</x:v>
+      <x:c r="P22" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="Q22" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="R22" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:18">
@@ -2253,10 +2214,10 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
         <x:v>17</x:v>
@@ -2268,7 +2229,7 @@
         <x:v>47</x:v>
       </x:c>
       <x:c r="K23" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="L23" s="0" t="s">
         <x:v>17</x:v>
@@ -2288,8 +2249,8 @@
       <x:c r="Q23" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="R23" s="4" t="s">
-        <x:v>66</x:v>
+      <x:c r="R23" s="2" t="s">
+        <x:v>49</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
